--- a/ABC突破切線圖表_20260610/ABC突破切線精選_20260610.xlsx
+++ b/ABC突破切線圖表_20260610/ABC突破切線精選_20260610.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -557,30 +557,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3576.TW</t>
+          <t>3162.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>精確</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>18.25</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>17.17</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>57171</v>
+        <v>5440</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>5521.TW</t>
+          <t>4721.TWO</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>工信</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>11.25</v>
+        <v>94.5</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>10.37</v>
+        <v>86.2</v>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.63%</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>10151</v>
+        <v>2999</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
@@ -625,32 +625,644 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2243.TW</t>
+          <t>2497.TW</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏旭-KY</t>
+          <t>怡利電</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30.8</v>
+        <v>65.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>29.3</v>
+        <v>61.9</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>3715.TW</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>定穎投控</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
           <t>5.12%</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>2126</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="F5" s="11" t="n">
+        <v>15834</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>3221.TWO</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>台嘉碩</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>28407</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>6831.TW</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>邁科</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>776</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>721.4299999999999</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>7.56%</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>1772</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7777.TWO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>能率亞洲</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>3162</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>6414.TW</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>樺漢</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>401</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>384.25</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>3363</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2484.TW</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>希華</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>9.22%</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>60687</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>3479.TWO</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>安勤</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6274.TWO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1615</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8707</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>3003.TW</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>健和興</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>1808</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6279.TWO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>胡連</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>122.17</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1391</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2476.TW</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>122.33</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>2.59%</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>6428</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6166.TW</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>凌華</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>5.77%</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2916</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>8050.TWO</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>廣積</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>2.45%</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>1641</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2891.TW</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>5.65%</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>53423</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>8110.TW</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>華東</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>10206</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2472.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>12.37%</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>2386</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>5386.TWO</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>548</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>509</v>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>7.66%</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1841</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>3044.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>468</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>6.84%</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>4547</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -661,6 +1273,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
